--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124268502</v>
+        <v>124270215</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,37 +1681,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460681</v>
+        <v>460675</v>
       </c>
       <c r="R10" t="n">
-        <v>7051894</v>
+        <v>7052082</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1740,7 +1745,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1750,12 +1755,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,41 +1771,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1919,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124270215</v>
+        <v>124266902</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,42 +1915,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460675</v>
+        <v>460854</v>
       </c>
       <c r="R12" t="n">
-        <v>7052082</v>
+        <v>7051492</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1999,7 +1974,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2009,12 +1984,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>På bark på gammal död gran med död topp i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2029,22 +2004,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124266902</v>
+        <v>124268502</v>
       </c>
       <c r="B13" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2057,21 +2032,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2081,13 +2056,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460854</v>
+        <v>460681</v>
       </c>
       <c r="R13" t="n">
-        <v>7051492</v>
+        <v>7051894</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2126,12 +2101,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på gammal död gran med död topp i gammal granskog</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,16 +2117,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124268185</v>
+        <v>124270076</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,32 +2881,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2915,13 +2914,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460745</v>
+        <v>460846</v>
       </c>
       <c r="R20" t="n">
-        <v>7051760</v>
+        <v>7051896</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2950,7 +2949,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2960,12 +2959,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,48 +2975,23 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124270076</v>
+        <v>124267659</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3050,29 +3024,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460846</v>
+        <v>460736</v>
       </c>
       <c r="R21" t="n">
-        <v>7051896</v>
+        <v>7051676</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3101,7 +3066,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3111,12 +3076,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3127,26 +3092,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124267659</v>
+        <v>124273118</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3159,21 +3149,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3183,13 +3173,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460736</v>
+        <v>460769</v>
       </c>
       <c r="R22" t="n">
-        <v>7051676</v>
+        <v>7051692</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3218,7 +3208,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3228,12 +3218,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,51 +3229,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124273118</v>
+        <v>124268185</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3301,37 +3261,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460769</v>
+        <v>460745</v>
       </c>
       <c r="R23" t="n">
-        <v>7051692</v>
+        <v>7051760</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3360,7 +3330,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3370,7 +3340,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3381,16 +3356,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124266865</v>
+        <v>124266590</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>77743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460869</v>
+        <v>460881</v>
       </c>
       <c r="R28" t="n">
-        <v>7051484</v>
+        <v>7051464</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På grov gammal sälg i gransumpskog</t>
+          <t>På grov gammal gran intill bäck</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3982,10 +3982,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124272867</v>
+        <v>124272441</v>
       </c>
       <c r="B29" t="n">
-        <v>78547</v>
+        <v>57209</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3998,34 +3998,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100063</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460773</v>
+        <v>460778</v>
       </c>
       <c r="R29" t="n">
-        <v>7052228</v>
+        <v>7052106</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4057,7 +4066,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4067,12 +4076,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4099,10 +4103,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124266590</v>
+        <v>124272795</v>
       </c>
       <c r="B30" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4115,34 +4119,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460881</v>
+        <v>460765</v>
       </c>
       <c r="R30" t="n">
-        <v>7051464</v>
+        <v>7052225</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4174,7 +4183,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4184,12 +4193,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På grov gammal gran intill bäck</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4204,22 +4213,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124272795</v>
+        <v>124266865</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4228,43 +4237,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460765</v>
+        <v>460869</v>
       </c>
       <c r="R31" t="n">
-        <v>7052225</v>
+        <v>7051484</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4296,7 +4300,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4306,12 +4310,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>På grov gammal sälg i gransumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4326,22 +4330,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124272441</v>
+        <v>124272867</v>
       </c>
       <c r="B32" t="n">
-        <v>57209</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4354,43 +4358,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100063</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460778</v>
+        <v>460773</v>
       </c>
       <c r="R32" t="n">
-        <v>7052106</v>
+        <v>7052228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4422,7 +4417,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4432,7 +4427,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4459,10 +4459,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124273916</v>
+        <v>124271818</v>
       </c>
       <c r="B33" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4471,46 +4471,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460823</v>
+        <v>460809</v>
       </c>
       <c r="R33" t="n">
-        <v>7051844</v>
+        <v>7052003</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4565,51 +4565,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124266881</v>
+        <v>124272685</v>
       </c>
       <c r="B34" t="n">
-        <v>79926</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4618,41 +4593,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460877</v>
+        <v>460814</v>
       </c>
       <c r="R34" t="n">
-        <v>7051476</v>
+        <v>7051693</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4681,7 +4661,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4691,7 +4671,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4706,22 +4691,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124267753</v>
+        <v>124266857</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,25 +4715,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4758,10 +4743,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460870</v>
+        <v>460846</v>
       </c>
       <c r="R35" t="n">
-        <v>7051547</v>
+        <v>7051488</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4793,7 +4778,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4803,7 +4788,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4818,22 +4808,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124269569</v>
+        <v>124270409</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4846,21 +4836,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4870,13 +4860,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460863</v>
+        <v>460829</v>
       </c>
       <c r="R36" t="n">
-        <v>7051810</v>
+        <v>7051949</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4905,7 +4895,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4915,7 +4905,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4930,22 +4925,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124266490</v>
+        <v>124273916</v>
       </c>
       <c r="B37" t="n">
-        <v>74901</v>
+        <v>79926</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4954,41 +4949,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460881</v>
+        <v>460823</v>
       </c>
       <c r="R37" t="n">
-        <v>7051457</v>
+        <v>7051844</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På senvuxen gran i gransumpskog</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5043,26 +5043,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124273176</v>
+        <v>124266881</v>
       </c>
       <c r="B38" t="n">
-        <v>74901</v>
+        <v>79926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5071,25 +5096,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5099,13 +5124,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460783</v>
+        <v>460877</v>
       </c>
       <c r="R38" t="n">
-        <v>7051674</v>
+        <v>7051476</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5134,7 +5159,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5144,12 +5169,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5164,22 +5184,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124266826</v>
+        <v>124267753</v>
       </c>
       <c r="B39" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5188,25 +5208,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5216,13 +5236,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460883</v>
+        <v>460870</v>
       </c>
       <c r="R39" t="n">
-        <v>7051481</v>
+        <v>7051547</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5251,7 +5271,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5261,7 +5281,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5276,22 +5296,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124267610</v>
+        <v>124269569</v>
       </c>
       <c r="B40" t="n">
-        <v>78891</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5304,21 +5324,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>283</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5328,13 +5348,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460872</v>
+        <v>460863</v>
       </c>
       <c r="R40" t="n">
-        <v>7051530</v>
+        <v>7051810</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5363,7 +5383,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5373,12 +5393,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På kvist på klen gran i äldre granskog</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5393,22 +5408,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124271818</v>
+        <v>124266490</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5421,42 +5436,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460809</v>
+        <v>460881</v>
       </c>
       <c r="R41" t="n">
-        <v>7052003</v>
+        <v>7051457</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,7 +5495,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5495,12 +5505,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På senvuxen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5515,22 +5525,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124272685</v>
+        <v>124273176</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5543,42 +5553,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460814</v>
+        <v>460783</v>
       </c>
       <c r="R42" t="n">
-        <v>7051693</v>
+        <v>7051674</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5607,7 +5612,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5617,12 +5622,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5637,22 +5642,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124266857</v>
+        <v>124266826</v>
       </c>
       <c r="B43" t="n">
-        <v>100279</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5665,21 +5670,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5689,13 +5694,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460846</v>
+        <v>460883</v>
       </c>
       <c r="R43" t="n">
-        <v>7051488</v>
+        <v>7051481</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5724,7 +5729,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5734,12 +5739,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5754,22 +5754,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124270409</v>
+        <v>124267610</v>
       </c>
       <c r="B44" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460829</v>
+        <v>460872</v>
       </c>
       <c r="R44" t="n">
-        <v>7051949</v>
+        <v>7051530</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På kvist på klen gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5871,22 +5871,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124269131</v>
+        <v>124273053</v>
       </c>
       <c r="B45" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,50 +5895,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460876</v>
+        <v>460745</v>
       </c>
       <c r="R45" t="n">
-        <v>7051779</v>
+        <v>7052123</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5977,7 +5977,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ymnigt och särskilt riktigt på många granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5988,23 +5993,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124273053</v>
+        <v>124269395</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -6037,29 +6067,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460745</v>
+        <v>460708</v>
       </c>
       <c r="R46" t="n">
-        <v>7052123</v>
+        <v>7051985</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6088,7 +6109,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6098,12 +6119,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ymnigt och särskilt riktigt på många granar.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6155,10 +6176,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124269395</v>
+        <v>124270612</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6171,37 +6192,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460708</v>
+        <v>460801</v>
       </c>
       <c r="R47" t="n">
-        <v>7051985</v>
+        <v>7051993</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6230,7 +6251,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6240,12 +6261,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6256,51 +6277,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124268557</v>
+        <v>124266776</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6313,39 +6309,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460824</v>
+        <v>460876</v>
       </c>
       <c r="R48" t="n">
-        <v>7051942</v>
+        <v>7051478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6377,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6387,12 +6378,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hackade efter hästmyror</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6407,19 +6393,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124269874</v>
+        <v>124268557</v>
       </c>
       <c r="B49" t="n">
         <v>57529</v>
@@ -6453,19 +6439,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460672</v>
+        <v>460824</v>
       </c>
       <c r="R49" t="n">
-        <v>7052266</v>
+        <v>7051942</v>
       </c>
       <c r="S49" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6494,7 +6485,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,7 +6495,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hackade efter hästmyror</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6519,22 +6515,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124269984</v>
+        <v>124269874</v>
       </c>
       <c r="B50" t="n">
-        <v>74769</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,41 +6539,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229653</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460724</v>
+        <v>460672</v>
       </c>
       <c r="R50" t="n">
-        <v>7051694</v>
+        <v>7052266</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6616,12 +6612,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6636,12 +6627,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6765,10 +6756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124270612</v>
+        <v>124269131</v>
       </c>
       <c r="B52" t="n">
-        <v>82597</v>
+        <v>57883</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6777,41 +6768,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460801</v>
+        <v>460876</v>
       </c>
       <c r="R52" t="n">
-        <v>7051993</v>
+        <v>7051779</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6850,12 +6850,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6882,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124266776</v>
+        <v>124269984</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>74769</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6894,25 +6889,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>229653</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6922,10 +6917,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460876</v>
+        <v>460724</v>
       </c>
       <c r="R53" t="n">
-        <v>7051478</v>
+        <v>7051694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6957,7 +6952,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6967,7 +6962,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6994,10 +6994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124270241</v>
+        <v>124271205</v>
       </c>
       <c r="B54" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7006,41 +7006,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460847</v>
+        <v>460596</v>
       </c>
       <c r="R54" t="n">
-        <v>7051906</v>
+        <v>7052315</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7069,7 +7074,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7079,12 +7084,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ymnigt på flera granar och med fertila bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7095,26 +7100,51 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124266973</v>
+        <v>124270241</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7123,51 +7153,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460809</v>
+        <v>460847</v>
       </c>
       <c r="R55" t="n">
-        <v>7051526</v>
+        <v>7051906</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7196,7 +7216,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7206,12 +7226,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7222,51 +7242,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124266798</v>
+        <v>124266973</v>
       </c>
       <c r="B56" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7275,31 +7270,36 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7308,13 +7308,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460814</v>
+        <v>460809</v>
       </c>
       <c r="R56" t="n">
-        <v>7051514</v>
+        <v>7051526</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7353,7 +7353,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7368,6 +7373,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7385,10 +7410,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124271205</v>
+        <v>124266798</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7397,43 +7422,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460596</v>
+        <v>460814</v>
       </c>
       <c r="R57" t="n">
-        <v>7052315</v>
+        <v>7051514</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -7465,7 +7490,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7475,12 +7500,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar och med fertila bålar.</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7495,26 +7515,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124267750</v>
+        <v>124266795</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460903</v>
+        <v>460859</v>
       </c>
       <c r="R64" t="n">
-        <v>7051534</v>
+        <v>7051485</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På marken i fuktig ravin med gammal granskog</t>
+          <t>På granlåga i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124268273</v>
+        <v>124267750</v>
       </c>
       <c r="B65" t="n">
-        <v>77743</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8463,25 +8463,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8491,13 +8491,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460865</v>
+        <v>460903</v>
       </c>
       <c r="R65" t="n">
-        <v>7051632</v>
+        <v>7051534</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog i ravin med underjordisk bäck</t>
+          <t>På marken i fuktig ravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8568,10 +8568,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124266795</v>
+        <v>124268273</v>
       </c>
       <c r="B66" t="n">
-        <v>90977</v>
+        <v>77743</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8580,25 +8580,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8608,13 +8608,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460859</v>
+        <v>460865</v>
       </c>
       <c r="R66" t="n">
-        <v>7051485</v>
+        <v>7051632</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På granlåga i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog i ravin med underjordisk bäck</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8678,17 +8678,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124267924</v>
+        <v>124266520</v>
       </c>
       <c r="B67" t="n">
-        <v>79919</v>
+        <v>57529</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8697,41 +8697,46 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460931</v>
+        <v>460783</v>
       </c>
       <c r="R67" t="n">
-        <v>7051552</v>
+        <v>7051478</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8760,7 +8765,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8770,7 +8775,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8781,26 +8791,51 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124271938</v>
+        <v>124267924</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8809,41 +8844,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>460584</v>
+        <v>460931</v>
       </c>
       <c r="R68" t="n">
-        <v>7052433</v>
+        <v>7051552</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8872,7 +8907,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8882,7 +8917,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8893,51 +8928,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124269152</v>
+        <v>124271938</v>
       </c>
       <c r="B69" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8950,37 +8960,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>460773</v>
+        <v>460584</v>
       </c>
       <c r="R69" t="n">
-        <v>7051617</v>
+        <v>7052433</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9009,7 +9019,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9019,12 +9029,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9035,23 +9040,48 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124267282</v>
+        <v>124269152</v>
       </c>
       <c r="B70" t="n">
         <v>74901</v>
@@ -9091,10 +9121,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>460867</v>
+        <v>460773</v>
       </c>
       <c r="R70" t="n">
-        <v>7051497</v>
+        <v>7051617</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9126,7 +9156,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9136,12 +9166,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gran 35 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9168,10 +9198,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124268628</v>
+        <v>124267282</v>
       </c>
       <c r="B71" t="n">
-        <v>79919</v>
+        <v>74901</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9180,25 +9210,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9208,13 +9238,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>460706</v>
+        <v>460867</v>
       </c>
       <c r="R71" t="n">
-        <v>7051944</v>
+        <v>7051497</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9243,7 +9273,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9253,7 +9283,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9264,31 +9299,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124268429</v>
+        <v>124268628</v>
       </c>
       <c r="B72" t="n">
-        <v>79892</v>
+        <v>79919</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9297,25 +9327,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9325,13 +9355,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>460855</v>
+        <v>460706</v>
       </c>
       <c r="R72" t="n">
-        <v>7051646</v>
+        <v>7051944</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9360,7 +9390,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9370,12 +9400,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog i ravin</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9386,26 +9411,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124266520</v>
+        <v>124268429</v>
       </c>
       <c r="B73" t="n">
-        <v>57529</v>
+        <v>79892</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9418,39 +9448,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>460783</v>
+        <v>460855</v>
       </c>
       <c r="R73" t="n">
-        <v>7051478</v>
+        <v>7051646</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9482,7 +9507,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9492,12 +9517,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På gammal sälg i gammal granskog i ravin</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9508,51 +9533,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124268215</v>
+        <v>124273453</v>
       </c>
       <c r="B74" t="n">
-        <v>77743</v>
+        <v>82597</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9565,21 +9565,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9589,13 +9589,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>460911</v>
+        <v>460826</v>
       </c>
       <c r="R74" t="n">
-        <v>7051589</v>
+        <v>7051956</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9634,12 +9634,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9654,22 +9649,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124268780</v>
+        <v>124274109</v>
       </c>
       <c r="B75" t="n">
-        <v>88359</v>
+        <v>79892</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,21 +9677,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9706,13 +9701,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>460823</v>
+        <v>460809</v>
       </c>
       <c r="R75" t="n">
-        <v>7051631</v>
+        <v>7051952</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9741,7 +9736,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9751,12 +9746,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På uppstickande rot på granlåga</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9771,22 +9766,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124274095</v>
+        <v>124268780</v>
       </c>
       <c r="B76" t="n">
-        <v>79927</v>
+        <v>88359</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9795,25 +9790,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9823,10 +9818,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>460864</v>
+        <v>460823</v>
       </c>
       <c r="R76" t="n">
-        <v>7051715</v>
+        <v>7051631</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9858,7 +9853,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9868,12 +9863,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På uppstickande rot på granlåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9888,22 +9883,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124272071</v>
+        <v>124274095</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9912,25 +9907,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9940,10 +9935,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>460768</v>
+        <v>460864</v>
       </c>
       <c r="R77" t="n">
-        <v>7051924</v>
+        <v>7051715</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9975,7 +9970,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9985,12 +9980,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt förekommande på granar</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10005,19 +10000,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124268956</v>
+        <v>124272071</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -10053,17 +10048,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>460777</v>
+        <v>460768</v>
       </c>
       <c r="R78" t="n">
-        <v>7052093</v>
+        <v>7051924</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10092,7 +10087,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10102,7 +10097,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10117,22 +10117,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124273453</v>
+        <v>124268956</v>
       </c>
       <c r="B79" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10145,34 +10145,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>460826</v>
+        <v>460777</v>
       </c>
       <c r="R79" t="n">
-        <v>7051956</v>
+        <v>7052093</v>
       </c>
       <c r="S79" t="n">
         <v>12</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10229,22 +10229,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124274109</v>
+        <v>124268215</v>
       </c>
       <c r="B80" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10257,21 +10257,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10281,13 +10281,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>460809</v>
+        <v>460911</v>
       </c>
       <c r="R80" t="n">
-        <v>7051952</v>
+        <v>7051589</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10346,12 +10346,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124268772</v>
+        <v>124273892</v>
       </c>
       <c r="B86" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10980,25 +10980,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>460856</v>
+        <v>460809</v>
       </c>
       <c r="R86" t="n">
-        <v>7051677</v>
+        <v>7051952</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11073,22 +11073,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124273892</v>
+        <v>124273924</v>
       </c>
       <c r="B87" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11101,24 +11101,29 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
@@ -11131,7 +11136,7 @@
         <v>7051952</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11160,7 +11165,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11170,12 +11175,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11202,10 +11202,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124273924</v>
+        <v>124269652</v>
       </c>
       <c r="B88" t="n">
-        <v>79926</v>
+        <v>79892</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11214,46 +11214,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>460809</v>
+        <v>460722</v>
       </c>
       <c r="R88" t="n">
-        <v>7051952</v>
+        <v>7051686</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11282,7 +11277,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11292,7 +11287,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11307,22 +11307,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124269652</v>
+        <v>124268772</v>
       </c>
       <c r="B89" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>460722</v>
+        <v>460856</v>
       </c>
       <c r="R89" t="n">
-        <v>7051686</v>
+        <v>7051677</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11404,12 +11404,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11424,12 +11424,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -12668,10 +12668,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124269445</v>
+        <v>124266711</v>
       </c>
       <c r="B99" t="n">
-        <v>79428</v>
+        <v>77743</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12684,21 +12684,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12708,10 +12708,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>460744</v>
+        <v>460885</v>
       </c>
       <c r="R99" t="n">
-        <v>7051655</v>
+        <v>7051465</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran 35 cm I diameter</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12785,10 +12785,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124268409</v>
+        <v>124266592</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12801,37 +12801,46 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>460806</v>
+        <v>460832</v>
       </c>
       <c r="R100" t="n">
-        <v>7051937</v>
+        <v>7051434</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12860,7 +12869,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12870,7 +12879,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12885,22 +12894,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin, August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124266718</v>
+        <v>124272912</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12913,37 +12922,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>460836</v>
+        <v>460810</v>
       </c>
       <c r="R101" t="n">
-        <v>7051472</v>
+        <v>7051669</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12972,7 +12986,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12982,7 +12996,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12993,51 +13012,26 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124270220</v>
+        <v>124272428</v>
       </c>
       <c r="B102" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13050,34 +13044,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>460847</v>
+        <v>460778</v>
       </c>
       <c r="R102" t="n">
-        <v>7051906</v>
+        <v>7052106</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13109,7 +13108,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13119,12 +13118,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13151,10 +13150,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124272912</v>
+        <v>124269445</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13167,42 +13166,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>460810</v>
+        <v>460744</v>
       </c>
       <c r="R103" t="n">
-        <v>7051669</v>
+        <v>7051655</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13231,7 +13225,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13241,12 +13235,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13261,22 +13255,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124272428</v>
+        <v>124268409</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13289,42 +13283,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>460778</v>
+        <v>460806</v>
       </c>
       <c r="R104" t="n">
-        <v>7052106</v>
+        <v>7051937</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13353,7 +13342,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13363,12 +13352,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13383,22 +13367,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124266592</v>
+        <v>124266718</v>
       </c>
       <c r="B105" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13411,46 +13395,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>460832</v>
+        <v>460836</v>
       </c>
       <c r="R105" t="n">
-        <v>7051434</v>
+        <v>7051472</v>
       </c>
       <c r="S105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13479,7 +13454,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13489,7 +13464,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13500,26 +13475,51 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124266711</v>
+        <v>124270220</v>
       </c>
       <c r="B106" t="n">
-        <v>77743</v>
+        <v>91299</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13532,21 +13532,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13556,10 +13556,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>460885</v>
+        <v>460847</v>
       </c>
       <c r="R106" t="n">
-        <v>7051465</v>
+        <v>7051906</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gammal gran 35 cm I diameter</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13621,12 +13621,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -14789,10 +14789,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124267176</v>
+        <v>124266993</v>
       </c>
       <c r="B116" t="n">
-        <v>74893</v>
+        <v>74769</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14801,25 +14801,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>308</v>
+        <v>229653</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14829,13 +14829,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460874</v>
+        <v>460875</v>
       </c>
       <c r="R116" t="n">
-        <v>7051455</v>
+        <v>7051489</v>
       </c>
       <c r="S116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14874,7 +14874,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg I gransumpskog</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14889,22 +14894,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124269110</v>
+        <v>124267176</v>
       </c>
       <c r="B117" t="n">
-        <v>91030</v>
+        <v>74893</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14917,51 +14922,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460750</v>
+        <v>460874</v>
       </c>
       <c r="R117" t="n">
-        <v>7051802</v>
+        <v>7051455</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14990,7 +14981,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15000,12 +14991,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Växer i en död smal gran.</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15016,51 +15002,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124272055</v>
+        <v>124269110</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15073,39 +15034,48 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460659</v>
+        <v>460750</v>
       </c>
       <c r="R118" t="n">
-        <v>7052433</v>
+        <v>7051802</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15137,7 +15107,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15147,12 +15117,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>Växer i en död smal gran.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15181,12 +15151,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15204,10 +15174,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124266993</v>
+        <v>124272055</v>
       </c>
       <c r="B119" t="n">
-        <v>74769</v>
+        <v>57529</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15216,38 +15186,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229653</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460875</v>
+        <v>460659</v>
       </c>
       <c r="R119" t="n">
-        <v>7051489</v>
+        <v>7052433</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15279,7 +15254,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,12 +15264,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På grov gammal sälg I gransumpskog</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15305,16 +15280,41 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124272055</v>
+        <v>124270433</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5428,39 +5428,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460659</v>
+        <v>460737</v>
       </c>
       <c r="R40" t="n">
-        <v>7052433</v>
+        <v>7051786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5492,7 +5487,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5502,12 +5497,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5518,48 +5513,23 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124269204</v>
+        <v>124273053</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5592,20 +5562,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460764</v>
+        <v>460745</v>
       </c>
       <c r="R41" t="n">
-        <v>7051615</v>
+        <v>7052123</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5634,7 +5613,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5644,12 +5623,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket rikligt förekommande på granar</t>
+          <t>Ymnigt och särskilt riktigt på många granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5660,23 +5639,48 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124270433</v>
+        <v>124272951</v>
       </c>
       <c r="B42" t="n">
         <v>74901</v>
@@ -5716,10 +5720,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460737</v>
+        <v>460795</v>
       </c>
       <c r="R42" t="n">
-        <v>7051786</v>
+        <v>7051765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5751,7 +5755,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5761,12 +5765,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran med hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5793,10 +5797,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124273053</v>
+        <v>124268772</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5809,46 +5813,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460745</v>
+        <v>460856</v>
       </c>
       <c r="R43" t="n">
-        <v>7052123</v>
+        <v>7051677</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5877,7 +5872,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5887,12 +5882,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnigt och särskilt riktigt på många granar.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5903,51 +5898,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124272951</v>
+        <v>124269204</v>
       </c>
       <c r="B44" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5960,21 +5930,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5984,10 +5954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460795</v>
+        <v>460764</v>
       </c>
       <c r="R44" t="n">
-        <v>7051765</v>
+        <v>7051615</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6019,7 +5989,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6029,12 +5999,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död gran med hackspår</t>
+          <t>Mycket rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6061,10 +6031,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124268772</v>
+        <v>124272055</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6077,34 +6047,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460856</v>
+        <v>460659</v>
       </c>
       <c r="R45" t="n">
-        <v>7051677</v>
+        <v>7052433</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6136,7 +6111,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6146,12 +6121,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6162,16 +6137,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124266771</v>
+        <v>124266724</v>
       </c>
       <c r="B47" t="n">
-        <v>78891</v>
+        <v>78547</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>283</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460836</v>
+        <v>460829</v>
       </c>
       <c r="R47" t="n">
-        <v>7051478</v>
+        <v>7051482</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På tunna grenar på gammal klen gran i gammal fuktig granskog</t>
+          <t>På kolad ved på gammal tallåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124266724</v>
+        <v>124266771</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>78891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6844,21 +6844,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460829</v>
+        <v>460836</v>
       </c>
       <c r="R51" t="n">
-        <v>7051482</v>
+        <v>7051478</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallåga i gammal granskog</t>
+          <t>På tunna grenar på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -13862,10 +13862,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124266592</v>
+        <v>124272014</v>
       </c>
       <c r="B108" t="n">
-        <v>56714</v>
+        <v>79919</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13874,47 +13874,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>460832</v>
+        <v>460654</v>
       </c>
       <c r="R108" t="n">
-        <v>7051434</v>
+        <v>7052478</v>
       </c>
       <c r="S108" t="n">
         <v>11</v>
@@ -13946,7 +13937,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13956,7 +13947,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13967,26 +13958,31 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124272014</v>
+        <v>124271595</v>
       </c>
       <c r="B109" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13995,25 +13991,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14023,13 +14019,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>460654</v>
+        <v>460618</v>
       </c>
       <c r="R109" t="n">
-        <v>7052478</v>
+        <v>7052330</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14058,7 +14054,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14068,7 +14064,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ymnigt och riktigt!</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14083,6 +14084,26 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14100,10 +14121,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124271595</v>
+        <v>124266592</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14116,37 +14137,46 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>460618</v>
+        <v>460832</v>
       </c>
       <c r="R110" t="n">
-        <v>7052330</v>
+        <v>7051434</v>
       </c>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14175,7 +14205,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14185,12 +14215,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ymnigt och riktigt!</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14201,51 +14226,26 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124269652</v>
+        <v>124267659</v>
       </c>
       <c r="B111" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14258,21 +14258,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14282,13 +14282,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>460722</v>
+        <v>460736</v>
       </c>
       <c r="R111" t="n">
-        <v>7051686</v>
+        <v>7051676</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14343,26 +14343,51 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124266993</v>
+        <v>124269652</v>
       </c>
       <c r="B112" t="n">
-        <v>74769</v>
+        <v>79892</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14371,25 +14396,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229653</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14399,10 +14424,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460875</v>
+        <v>460722</v>
       </c>
       <c r="R112" t="n">
-        <v>7051489</v>
+        <v>7051686</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14434,7 +14459,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14444,12 +14469,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>På grov gammal sälg I gransumpskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14469,17 +14494,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124267659</v>
+        <v>124266993</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>74769</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14488,25 +14513,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229653</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14516,13 +14541,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460736</v>
+        <v>460875</v>
       </c>
       <c r="R113" t="n">
-        <v>7051676</v>
+        <v>7051489</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14551,7 +14576,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14561,12 +14586,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På grov gammal sälg I gransumpskog</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14577,41 +14602,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124274274</v>
+        <v>124271872</v>
       </c>
       <c r="B116" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14898,42 +14898,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460882</v>
+        <v>460775</v>
       </c>
       <c r="R116" t="n">
-        <v>7051627</v>
+        <v>7051981</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14962,7 +14957,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14972,12 +14967,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14988,51 +14983,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124271872</v>
+        <v>124274274</v>
       </c>
       <c r="B117" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15045,37 +15015,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460775</v>
+        <v>460882</v>
       </c>
       <c r="R117" t="n">
-        <v>7051981</v>
+        <v>7051627</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -15104,7 +15079,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15114,12 +15089,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15130,16 +15105,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124267103</v>
+        <v>124272071</v>
       </c>
       <c r="B5" t="n">
-        <v>79066</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,25 +1068,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460866</v>
+        <v>460768</v>
       </c>
       <c r="R5" t="n">
-        <v>7051496</v>
+        <v>7051924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,17 +1166,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124272071</v>
+        <v>124267103</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79066</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1185,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460768</v>
+        <v>460866</v>
       </c>
       <c r="R6" t="n">
-        <v>7051924</v>
+        <v>7051496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande på granar</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124273037</v>
+        <v>124273916</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>79926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2693,46 +2693,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460711</v>
+        <v>460823</v>
       </c>
       <c r="R18" t="n">
-        <v>7052086</v>
+        <v>7051844</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2787,26 +2787,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124266776</v>
+        <v>124273896</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2815,41 +2840,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460876</v>
+        <v>460818</v>
       </c>
       <c r="R19" t="n">
-        <v>7051478</v>
+        <v>7051847</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2878,7 +2908,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2888,7 +2918,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2899,26 +2934,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124274109</v>
+        <v>124272441</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>57209</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,37 +2991,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100063</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460809</v>
+        <v>460778</v>
       </c>
       <c r="R20" t="n">
-        <v>7051952</v>
+        <v>7052106</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2990,7 +3059,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3000,12 +3069,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3020,65 +3084,70 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124270241</v>
+        <v>124270215</v>
       </c>
       <c r="B21" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460847</v>
+        <v>460675</v>
       </c>
       <c r="R21" t="n">
-        <v>7051906</v>
+        <v>7052082</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,7 +3176,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3117,12 +3186,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3137,22 +3206,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124273916</v>
+        <v>124272867</v>
       </c>
       <c r="B22" t="n">
-        <v>79926</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3161,46 +3230,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460823</v>
+        <v>460773</v>
       </c>
       <c r="R22" t="n">
-        <v>7051844</v>
+        <v>7052228</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3229,7 +3293,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3239,12 +3303,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>På kolad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3255,51 +3319,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124273896</v>
+        <v>124273037</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>88359</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3308,46 +3347,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460818</v>
+        <v>460711</v>
       </c>
       <c r="R23" t="n">
-        <v>7051847</v>
+        <v>7052086</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3376,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3386,12 +3425,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3402,51 +3441,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124272441</v>
+        <v>124266776</v>
       </c>
       <c r="B24" t="n">
-        <v>57209</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3459,43 +3473,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100063</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460778</v>
+        <v>460876</v>
       </c>
       <c r="R24" t="n">
-        <v>7052106</v>
+        <v>7051478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3527,7 +3532,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3537,7 +3542,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3552,22 +3557,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124270215</v>
+        <v>124274109</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3580,42 +3585,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460675</v>
+        <v>460809</v>
       </c>
       <c r="R25" t="n">
-        <v>7052082</v>
+        <v>7051952</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3674,22 +3674,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124272867</v>
+        <v>124270241</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>91457</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3698,25 +3698,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460773</v>
+        <v>460847</v>
       </c>
       <c r="R26" t="n">
-        <v>7052228</v>
+        <v>7051906</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5412,10 +5412,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124270433</v>
+        <v>124272055</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5428,34 +5428,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460737</v>
+        <v>460659</v>
       </c>
       <c r="R40" t="n">
-        <v>7051786</v>
+        <v>7052433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5487,7 +5492,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5497,12 +5502,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5513,23 +5518,48 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124273053</v>
+        <v>124269204</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5562,29 +5592,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460745</v>
+        <v>460764</v>
       </c>
       <c r="R41" t="n">
-        <v>7052123</v>
+        <v>7051615</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,7 +5634,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5623,12 +5644,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnigt och särskilt riktigt på många granar.</t>
+          <t>Mycket rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5639,48 +5660,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124272951</v>
+        <v>124270433</v>
       </c>
       <c r="B42" t="n">
         <v>74901</v>
@@ -5720,10 +5716,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460795</v>
+        <v>460737</v>
       </c>
       <c r="R42" t="n">
-        <v>7051765</v>
+        <v>7051786</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5755,7 +5751,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5765,12 +5761,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död gran med hackspår</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5797,10 +5793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124268772</v>
+        <v>124273053</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5813,37 +5809,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460856</v>
+        <v>460745</v>
       </c>
       <c r="R43" t="n">
-        <v>7051677</v>
+        <v>7052123</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5872,7 +5877,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5882,12 +5887,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ymnigt och särskilt riktigt på många granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5898,26 +5903,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124269204</v>
+        <v>124272951</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5930,21 +5960,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5954,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460764</v>
+        <v>460795</v>
       </c>
       <c r="R44" t="n">
-        <v>7051615</v>
+        <v>7051765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5989,7 +6019,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5999,12 +6029,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Mycket rikligt förekommande på granar</t>
+          <t>På död gran med hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6031,10 +6061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124272055</v>
+        <v>124268772</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6047,39 +6077,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460659</v>
+        <v>460856</v>
       </c>
       <c r="R45" t="n">
-        <v>7052433</v>
+        <v>7051677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6111,7 +6136,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6121,12 +6146,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hackspår.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6137,41 +6162,16 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7662,10 +7662,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124266865</v>
+        <v>124269673</v>
       </c>
       <c r="B58" t="n">
-        <v>79851</v>
+        <v>79926</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460869</v>
+        <v>460721</v>
       </c>
       <c r="R58" t="n">
-        <v>7051484</v>
+        <v>7051684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På grov gammal sälg i gransumpskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7779,10 +7779,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124269131</v>
+        <v>124274112</v>
       </c>
       <c r="B59" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7791,50 +7791,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460876</v>
+        <v>460851</v>
       </c>
       <c r="R59" t="n">
-        <v>7051779</v>
+        <v>7051715</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7873,7 +7873,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7884,26 +7889,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124269673</v>
+        <v>124266902</v>
       </c>
       <c r="B60" t="n">
-        <v>79926</v>
+        <v>88359</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7912,25 +7942,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7940,13 +7970,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460721</v>
+        <v>460854</v>
       </c>
       <c r="R60" t="n">
-        <v>7051684</v>
+        <v>7051492</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7975,7 +8005,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7985,12 +8015,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på gammal död gran med död topp i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8005,26 +8035,26 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124274112</v>
+        <v>124272428</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8033,46 +8063,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460851</v>
+        <v>460778</v>
       </c>
       <c r="R61" t="n">
-        <v>7051715</v>
+        <v>7052106</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8101,7 +8127,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8111,12 +8137,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8127,55 +8153,30 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124266902</v>
+        <v>124269906</v>
       </c>
       <c r="B62" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8184,37 +8185,47 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460854</v>
+        <v>460698</v>
       </c>
       <c r="R62" t="n">
-        <v>7051492</v>
+        <v>7052021</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8243,7 +8254,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8253,12 +8264,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på gammal död gran med död topp i gammal granskog</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8269,26 +8280,51 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124272428</v>
+        <v>124269131</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8297,20 +8333,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8318,10 +8354,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8330,13 +8370,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460778</v>
+        <v>460876</v>
       </c>
       <c r="R63" t="n">
-        <v>7052106</v>
+        <v>7051779</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8365,7 +8405,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8375,12 +8415,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8395,22 +8430,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124269906</v>
+        <v>124266865</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8419,48 +8454,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460698</v>
+        <v>460869</v>
       </c>
       <c r="R64" t="n">
-        <v>7052021</v>
+        <v>7051484</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8492,7 +8517,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8502,12 +8527,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>På grov gammal sälg i gransumpskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8518,41 +8543,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9534,14 +9534,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124272422</v>
+        <v>124268252</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9550,42 +9550,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>460738</v>
+        <v>460924</v>
       </c>
       <c r="R73" t="n">
-        <v>7052399</v>
+        <v>7051476</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ymnigt, rikligt och fertilt.</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9640,48 +9640,23 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124267409</v>
+        <v>124272422</v>
       </c>
       <c r="B74" t="n">
         <v>78810</v>
@@ -9715,19 +9690,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>460780</v>
+        <v>460738</v>
       </c>
       <c r="R74" t="n">
-        <v>7051604</v>
+        <v>7052399</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9756,7 +9736,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9766,12 +9746,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ymnigt, rikligt och fertilt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9823,10 +9803,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124268628</v>
+        <v>124267409</v>
       </c>
       <c r="B75" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9835,25 +9815,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9863,10 +9843,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>460706</v>
+        <v>460780</v>
       </c>
       <c r="R75" t="n">
-        <v>7051944</v>
+        <v>7051604</v>
       </c>
       <c r="S75" t="n">
         <v>7</v>
@@ -9898,7 +9878,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9908,7 +9888,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9923,6 +9908,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9940,10 +9945,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124268252</v>
+        <v>124268628</v>
       </c>
       <c r="B76" t="n">
-        <v>57513</v>
+        <v>79919</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9952,46 +9957,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>460924</v>
+        <v>460706</v>
       </c>
       <c r="R76" t="n">
-        <v>7051476</v>
+        <v>7051944</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10030,12 +10030,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:42</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10046,16 +10041,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124268502</v>
+        <v>124266711</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10195,21 +10195,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10219,13 +10219,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>460681</v>
+        <v>460885</v>
       </c>
       <c r="R78" t="n">
-        <v>7051894</v>
+        <v>7051465</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10264,12 +10264,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>På gammal gran 35 cm I diameter</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10280,51 +10280,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124266826</v>
+        <v>124268273</v>
       </c>
       <c r="B79" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10333,25 +10308,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10361,13 +10336,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>460883</v>
+        <v>460865</v>
       </c>
       <c r="R79" t="n">
-        <v>7051481</v>
+        <v>7051632</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10396,7 +10371,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10406,7 +10381,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog i ravin med underjordisk bäck</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10421,22 +10401,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124272148</v>
+        <v>124267610</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10449,42 +10429,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>460703</v>
+        <v>460872</v>
       </c>
       <c r="R80" t="n">
-        <v>7052473</v>
+        <v>7051530</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10513,7 +10488,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10523,7 +10498,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På kvist på klen gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10534,51 +10514,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124267610</v>
+        <v>124268502</v>
       </c>
       <c r="B81" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10591,21 +10546,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10615,13 +10570,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>460872</v>
+        <v>460681</v>
       </c>
       <c r="R81" t="n">
-        <v>7051530</v>
+        <v>7051894</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10650,7 +10605,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10660,12 +10615,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På kvist på klen gran i äldre granskog</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10676,26 +10631,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124266711</v>
+        <v>124266826</v>
       </c>
       <c r="B82" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10704,25 +10684,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10732,13 +10712,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>460885</v>
+        <v>460883</v>
       </c>
       <c r="R82" t="n">
-        <v>7051465</v>
+        <v>7051481</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10767,7 +10747,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10777,12 +10757,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal gran 35 cm I diameter</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10797,22 +10772,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124268273</v>
+        <v>124272148</v>
       </c>
       <c r="B83" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10825,34 +10800,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>460865</v>
+        <v>460703</v>
       </c>
       <c r="R83" t="n">
-        <v>7051632</v>
+        <v>7052473</v>
       </c>
       <c r="S83" t="n">
         <v>8</v>
@@ -10884,7 +10864,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10894,12 +10874,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog i ravin med underjordisk bäck</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10910,16 +10885,41 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15146,50 +15146,55 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124267750</v>
+        <v>124272795</v>
       </c>
       <c r="B118" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460903</v>
+        <v>460765</v>
       </c>
       <c r="R118" t="n">
-        <v>7051534</v>
+        <v>7052225</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15221,7 +15226,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15231,12 +15236,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På marken i fuktig ravin med gammal granskog</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15256,17 +15261,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124269155</v>
+        <v>124266857</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15275,41 +15280,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460637</v>
+        <v>460846</v>
       </c>
       <c r="R119" t="n">
-        <v>7052403</v>
+        <v>7051488</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15338,7 +15343,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15348,7 +15353,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15363,19 +15373,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124266857</v>
+        <v>124267750</v>
       </c>
       <c r="B120" t="n">
         <v>100279</v>
@@ -15415,10 +15425,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460846</v>
+        <v>460903</v>
       </c>
       <c r="R120" t="n">
-        <v>7051488</v>
+        <v>7051534</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15450,7 +15460,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15460,12 +15470,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>På marken i fuktig ravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15485,7 +15495,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -15726,10 +15736,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124272795</v>
+        <v>124269155</v>
       </c>
       <c r="B123" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15742,42 +15752,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460765</v>
+        <v>460637</v>
       </c>
       <c r="R123" t="n">
-        <v>7052225</v>
+        <v>7052403</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15806,7 +15811,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15816,12 +15821,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15836,12 +15836,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124267409</v>
+        <v>124266871</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,25 +2213,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460780</v>
+        <v>460877</v>
       </c>
       <c r="R15" t="n">
-        <v>7051604</v>
+        <v>7051476</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,51 +2297,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124266865</v>
+        <v>124268772</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,25 +2325,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2383,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460869</v>
+        <v>460856</v>
       </c>
       <c r="R16" t="n">
-        <v>7051484</v>
+        <v>7051677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2418,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,12 +2398,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grov gammal sälg i gransumpskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,22 +2418,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124266871</v>
+        <v>124269984</v>
       </c>
       <c r="B17" t="n">
-        <v>79927</v>
+        <v>74769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,25 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>229653</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,13 +2470,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460877</v>
+        <v>460724</v>
       </c>
       <c r="R17" t="n">
-        <v>7051476</v>
+        <v>7051694</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2535,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2545,7 +2515,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,19 +2535,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124268502</v>
+        <v>124267409</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2612,13 +2587,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460681</v>
+        <v>460780</v>
       </c>
       <c r="R18" t="n">
-        <v>7051894</v>
+        <v>7051604</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2647,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2632,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2714,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124269975</v>
+        <v>124268502</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2730,56 +2705,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460676</v>
+        <v>460681</v>
       </c>
       <c r="R19" t="n">
-        <v>7052009</v>
+        <v>7051894</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2808,7 +2764,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2818,12 +2774,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mellanlandade, sjöng, och flög vidare inom sitt revir.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,6 +2794,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2855,10 +2831,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124268772</v>
+        <v>124269975</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,34 +2847,53 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460856</v>
+        <v>460676</v>
       </c>
       <c r="R20" t="n">
-        <v>7051677</v>
+        <v>7052009</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2940,12 +2935,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Mellanlandade, sjöng, och flög vidare inom sitt revir.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,26 +2951,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124269984</v>
+        <v>124266865</v>
       </c>
       <c r="B21" t="n">
-        <v>74769</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,25 +2984,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229653</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460724</v>
+        <v>460869</v>
       </c>
       <c r="R21" t="n">
-        <v>7051694</v>
+        <v>7051484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
+          <t>På grov gammal sälg i gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3089,10 +3089,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124268628</v>
+        <v>124274109</v>
       </c>
       <c r="B22" t="n">
-        <v>79919</v>
+        <v>79892</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3101,25 +3101,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460706</v>
+        <v>460809</v>
       </c>
       <c r="R22" t="n">
-        <v>7051944</v>
+        <v>7051952</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3174,7 +3174,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,31 +3190,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124274109</v>
+        <v>124273054</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460809</v>
+        <v>460777</v>
       </c>
       <c r="R23" t="n">
-        <v>7051952</v>
+        <v>7051731</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3311,22 +3311,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124273054</v>
+        <v>124269395</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3339,37 +3339,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460777</v>
+        <v>460708</v>
       </c>
       <c r="R24" t="n">
-        <v>7051731</v>
+        <v>7051985</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3424,26 +3424,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124269395</v>
+        <v>124268628</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3452,41 +3477,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460708</v>
+        <v>460706</v>
       </c>
       <c r="R25" t="n">
-        <v>7051985</v>
+        <v>7051944</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3515,7 +3540,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3525,12 +3550,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3545,26 +3565,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124272775</v>
+        <v>124273037</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3598,34 +3598,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460810</v>
+        <v>460711</v>
       </c>
       <c r="R26" t="n">
-        <v>7051824</v>
+        <v>7052086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3657,7 +3662,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3667,7 +3672,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3682,22 +3692,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124268409</v>
+        <v>124272644</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3710,37 +3720,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460806</v>
+        <v>460793</v>
       </c>
       <c r="R27" t="n">
-        <v>7051937</v>
+        <v>7051847</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3769,7 +3779,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3779,7 +3789,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,22 +3809,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124269110</v>
+        <v>124269155</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3822,51 +3837,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460750</v>
+        <v>460637</v>
       </c>
       <c r="R28" t="n">
-        <v>7051802</v>
+        <v>7052403</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3895,7 +3896,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3905,12 +3906,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer i en död smal gran.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3921,51 +3917,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124266902</v>
+        <v>124272775</v>
       </c>
       <c r="B29" t="n">
-        <v>88359</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,21 +3949,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4002,13 +3973,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460854</v>
+        <v>460810</v>
       </c>
       <c r="R29" t="n">
-        <v>7051492</v>
+        <v>7051824</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4037,7 +4008,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4047,12 +4018,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark på gammal död gran med död topp i gammal granskog</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4067,19 +4033,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124269155</v>
+        <v>124268409</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -4115,17 +4081,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460637</v>
+        <v>460806</v>
       </c>
       <c r="R30" t="n">
-        <v>7052403</v>
+        <v>7051937</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4154,7 +4120,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4164,7 +4130,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4191,10 +4157,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124273037</v>
+        <v>124269110</v>
       </c>
       <c r="B31" t="n">
-        <v>88359</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4207,24 +4173,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4236,10 +4211,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460711</v>
+        <v>460750</v>
       </c>
       <c r="R31" t="n">
-        <v>7052086</v>
+        <v>7051802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4271,7 +4246,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4281,12 +4256,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Växer i en död smal gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4297,26 +4272,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124272644</v>
+        <v>124266902</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4329,21 +4329,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4353,13 +4353,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460793</v>
+        <v>460854</v>
       </c>
       <c r="R32" t="n">
-        <v>7051847</v>
+        <v>7051492</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på gammal död gran med död topp i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4418,12 +4418,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5033,10 +5033,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124266795</v>
+        <v>124267282</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>74901</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5045,25 +5045,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460859</v>
+        <v>460867</v>
       </c>
       <c r="R38" t="n">
-        <v>7051485</v>
+        <v>7051497</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På granlåga i gammal fuktig granskog</t>
+          <t>På gran 35 cm i diameter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5138,22 +5138,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124266857</v>
+        <v>124267659</v>
       </c>
       <c r="B39" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5162,25 +5162,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5190,13 +5190,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460846</v>
+        <v>460736</v>
       </c>
       <c r="R39" t="n">
-        <v>7051488</v>
+        <v>7051676</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På marken i fuktig gammal granskog</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,26 +5251,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124267282</v>
+        <v>124266795</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>90977</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5279,25 +5304,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5307,10 +5332,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460867</v>
+        <v>460859</v>
       </c>
       <c r="R40" t="n">
-        <v>7051497</v>
+        <v>7051485</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5342,7 +5367,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5352,12 +5377,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran 35 cm i diameter</t>
+          <t>På granlåga i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,22 +5397,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124267659</v>
+        <v>124266857</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5396,25 +5421,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5424,13 +5449,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460736</v>
+        <v>460846</v>
       </c>
       <c r="R41" t="n">
-        <v>7051676</v>
+        <v>7051488</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5459,7 +5484,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5469,12 +5494,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På marken i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5485,41 +5510,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124274384</v>
+        <v>124267924</v>
       </c>
       <c r="B43" t="n">
-        <v>77743</v>
+        <v>79919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5685,25 +5685,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460877</v>
+        <v>460931</v>
       </c>
       <c r="R43" t="n">
-        <v>7051584</v>
+        <v>7051552</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124267924</v>
+        <v>124273892</v>
       </c>
       <c r="B44" t="n">
-        <v>79919</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5825,13 +5825,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460931</v>
+        <v>460809</v>
       </c>
       <c r="R44" t="n">
-        <v>7051552</v>
+        <v>7051952</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5870,7 +5870,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5897,10 +5902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124273892</v>
+        <v>124274384</v>
       </c>
       <c r="B45" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5909,25 +5914,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5937,13 +5942,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460809</v>
+        <v>460877</v>
       </c>
       <c r="R45" t="n">
-        <v>7051952</v>
+        <v>7051584</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5972,7 +5977,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5982,12 +5987,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6360,10 +6360,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124269623</v>
+        <v>124267176</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>74893</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6376,34 +6376,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460672</v>
+        <v>460874</v>
       </c>
       <c r="R49" t="n">
-        <v>7052266</v>
+        <v>7051455</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6460,22 +6460,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124267176</v>
+        <v>124269628</v>
       </c>
       <c r="B50" t="n">
-        <v>74893</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6488,37 +6488,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460874</v>
+        <v>460689</v>
       </c>
       <c r="R50" t="n">
-        <v>7051455</v>
+        <v>7052027</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6547,7 +6552,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6557,7 +6562,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt, där vissa bålar är fertila.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6568,23 +6578,48 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124269628</v>
+        <v>124269623</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6618,24 +6653,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460689</v>
+        <v>460672</v>
       </c>
       <c r="R51" t="n">
-        <v>7052027</v>
+        <v>7052266</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6664,7 +6694,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6674,12 +6704,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt, där vissa bålar är fertila.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6690,51 +6715,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124266592</v>
+        <v>124273176</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6747,46 +6747,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460832</v>
+        <v>460783</v>
       </c>
       <c r="R52" t="n">
-        <v>7051434</v>
+        <v>7051674</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6815,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6825,7 +6816,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6840,22 +6836,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124273176</v>
+        <v>124268956</v>
       </c>
       <c r="B53" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6868,37 +6864,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460783</v>
+        <v>460777</v>
       </c>
       <c r="R53" t="n">
-        <v>7051674</v>
+        <v>7052093</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6927,7 +6923,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6937,12 +6933,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6957,22 +6948,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124268956</v>
+        <v>124266592</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6985,37 +6976,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460777</v>
+        <v>460832</v>
       </c>
       <c r="R54" t="n">
-        <v>7052093</v>
+        <v>7051434</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7069,12 +7069,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124268557</v>
+        <v>124273727</v>
       </c>
       <c r="B67" t="n">
-        <v>57529</v>
+        <v>88359</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8623,27 +8623,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8652,13 +8652,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460824</v>
+        <v>460800</v>
       </c>
       <c r="R67" t="n">
-        <v>7051942</v>
+        <v>7051879</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Hackade efter hästmyror</t>
+          <t>På stambasen an en död stående gran som lutar mot en levande gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8713,26 +8713,51 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124269673</v>
+        <v>124272867</v>
       </c>
       <c r="B68" t="n">
-        <v>79926</v>
+        <v>78547</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8741,25 +8766,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8769,10 +8794,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>460721</v>
+        <v>460773</v>
       </c>
       <c r="R68" t="n">
-        <v>7051684</v>
+        <v>7052228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8804,7 +8829,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8814,12 +8839,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8834,22 +8859,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124266696</v>
+        <v>124268557</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8862,34 +8887,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>460886</v>
+        <v>460824</v>
       </c>
       <c r="R69" t="n">
-        <v>7051482</v>
+        <v>7051942</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8921,7 +8951,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8931,12 +8961,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt förekommande på granar</t>
+          <t>Hackade efter hästmyror</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8951,22 +8981,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124273727</v>
+        <v>124269673</v>
       </c>
       <c r="B70" t="n">
-        <v>88359</v>
+        <v>79926</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8975,46 +9005,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>460800</v>
+        <v>460721</v>
       </c>
       <c r="R70" t="n">
-        <v>7051879</v>
+        <v>7051684</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9043,7 +9068,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9053,12 +9078,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På stambasen an en död stående gran som lutar mot en levande gran.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9069,51 +9094,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124270409</v>
+        <v>124266696</v>
       </c>
       <c r="B71" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9126,21 +9126,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>460829</v>
+        <v>460886</v>
       </c>
       <c r="R71" t="n">
-        <v>7051949</v>
+        <v>7051482</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9215,22 +9215,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124272867</v>
+        <v>124270409</v>
       </c>
       <c r="B72" t="n">
-        <v>78547</v>
+        <v>77743</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9243,21 +9243,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>460773</v>
+        <v>460829</v>
       </c>
       <c r="R72" t="n">
-        <v>7052228</v>
+        <v>7051949</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124272071</v>
+        <v>124272422</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -10016,19 +10016,24 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>460768</v>
+        <v>460738</v>
       </c>
       <c r="R78" t="n">
-        <v>7051924</v>
+        <v>7052399</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10057,7 +10062,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10067,12 +10072,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt förekommande på granar</t>
+          <t>Ymnigt, rikligt och fertilt.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10083,16 +10088,41 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -10216,10 +10246,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124272422</v>
+        <v>124269569</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10232,42 +10262,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>460738</v>
+        <v>460863</v>
       </c>
       <c r="R80" t="n">
-        <v>7052399</v>
+        <v>7051810</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10296,7 +10321,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10306,12 +10331,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ymnigt, rikligt och fertilt.</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10322,51 +10342,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124269569</v>
+        <v>124266826</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10375,25 +10370,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10403,13 +10398,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>460863</v>
+        <v>460883</v>
       </c>
       <c r="R81" t="n">
-        <v>7051810</v>
+        <v>7051481</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10438,7 +10433,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10448,7 +10443,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10468,17 +10463,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124266826</v>
+        <v>124272071</v>
       </c>
       <c r="B82" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10487,25 +10482,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10515,13 +10510,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>460883</v>
+        <v>460768</v>
       </c>
       <c r="R82" t="n">
-        <v>7051481</v>
+        <v>7051924</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10550,7 +10545,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10560,7 +10555,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande på granar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10575,22 +10575,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124272396</v>
+        <v>124268342</v>
       </c>
       <c r="B83" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10603,34 +10603,44 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>460801</v>
+        <v>460688</v>
       </c>
       <c r="R83" t="n">
-        <v>7051922</v>
+        <v>7051787</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10662,7 +10672,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10672,12 +10682,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10688,26 +10698,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124268342</v>
+        <v>124270241</v>
       </c>
       <c r="B84" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10716,48 +10751,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>460688</v>
+        <v>460847</v>
       </c>
       <c r="R84" t="n">
-        <v>7051787</v>
+        <v>7051906</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10789,7 +10814,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10799,12 +10824,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10815,51 +10840,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124270241</v>
+        <v>124272396</v>
       </c>
       <c r="B85" t="n">
-        <v>91457</v>
+        <v>74901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10868,25 +10868,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>460847</v>
+        <v>460801</v>
       </c>
       <c r="R85" t="n">
-        <v>7051906</v>
+        <v>7051922</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10961,12 +10961,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -12218,10 +12218,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124272441</v>
+        <v>124266993</v>
       </c>
       <c r="B96" t="n">
-        <v>57209</v>
+        <v>74769</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12230,47 +12230,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100063</v>
+        <v>229653</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>460778</v>
+        <v>460875</v>
       </c>
       <c r="R96" t="n">
-        <v>7052106</v>
+        <v>7051489</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12302,7 +12293,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12312,7 +12303,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg I gransumpskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12327,22 +12323,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124269152</v>
+        <v>124266711</v>
       </c>
       <c r="B97" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12355,21 +12351,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12379,10 +12375,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>460773</v>
+        <v>460885</v>
       </c>
       <c r="R97" t="n">
-        <v>7051617</v>
+        <v>7051465</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12414,7 +12410,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12424,12 +12420,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran 35 cm I diameter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12456,10 +12452,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124266993</v>
+        <v>124266771</v>
       </c>
       <c r="B98" t="n">
-        <v>74769</v>
+        <v>78891</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12468,25 +12464,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229653</v>
+        <v>283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12496,10 +12492,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>460875</v>
+        <v>460836</v>
       </c>
       <c r="R98" t="n">
-        <v>7051489</v>
+        <v>7051478</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12531,7 +12527,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12541,12 +12537,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På grov gammal sälg I gransumpskog</t>
+          <t>På tunna grenar på gammal klen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12561,22 +12557,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124266711</v>
+        <v>124266520</v>
       </c>
       <c r="B99" t="n">
-        <v>77743</v>
+        <v>57529</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12589,34 +12585,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>460885</v>
+        <v>460783</v>
       </c>
       <c r="R99" t="n">
-        <v>7051465</v>
+        <v>7051478</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12648,7 +12649,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12658,12 +12659,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gammal gran 35 cm I diameter</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12674,26 +12675,51 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124266771</v>
+        <v>124273896</v>
       </c>
       <c r="B100" t="n">
-        <v>78891</v>
+        <v>79920</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12702,41 +12728,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>460836</v>
+        <v>460818</v>
       </c>
       <c r="R100" t="n">
-        <v>7051478</v>
+        <v>7051847</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12765,7 +12796,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12775,12 +12806,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På tunna grenar på gammal klen gran i gammal fuktig granskog</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12791,26 +12822,51 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124266520</v>
+        <v>124270532</v>
       </c>
       <c r="B101" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12823,42 +12879,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>460783</v>
+        <v>460654</v>
       </c>
       <c r="R101" t="n">
-        <v>7051478</v>
+        <v>7052144</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12887,7 +12943,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12897,12 +12953,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12931,12 +12987,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -12954,10 +13010,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124273896</v>
+        <v>124272441</v>
       </c>
       <c r="B102" t="n">
-        <v>79920</v>
+        <v>57209</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12966,46 +13022,50 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>100063</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>460818</v>
+        <v>460778</v>
       </c>
       <c r="R102" t="n">
-        <v>7051847</v>
+        <v>7052106</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13034,7 +13094,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13044,12 +13104,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13060,51 +13115,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124270532</v>
+        <v>124269152</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13117,42 +13147,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>460654</v>
+        <v>460773</v>
       </c>
       <c r="R103" t="n">
-        <v>7052144</v>
+        <v>7051617</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13181,7 +13206,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13191,12 +13216,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Fertil med apothecier.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13207,41 +13232,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124267188</v>
+        <v>124274274</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14490,24 +14490,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460766</v>
+        <v>460882</v>
       </c>
       <c r="R114" t="n">
-        <v>7051531</v>
+        <v>7051627</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14536,7 +14531,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14546,12 +14541,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14603,7 +14598,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124274274</v>
+        <v>124267188</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14642,19 +14637,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460882</v>
+        <v>460766</v>
       </c>
       <c r="R115" t="n">
-        <v>7051627</v>
+        <v>7051531</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124272014</v>
+        <v>124273054</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,41 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460654</v>
+        <v>460777</v>
       </c>
       <c r="R5" t="n">
-        <v>7052478</v>
+        <v>7051731</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,31 +1122,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124273054</v>
+        <v>124274542</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,37 +1154,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460777</v>
+        <v>460913</v>
       </c>
       <c r="R6" t="n">
-        <v>7051731</v>
+        <v>7051490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,26 +1243,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124274542</v>
+        <v>124272014</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,50 +1286,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460913</v>
+        <v>460654</v>
       </c>
       <c r="R7" t="n">
-        <v>7051490</v>
+        <v>7052478</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,16 +1374,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -7490,10 +7490,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124268557</v>
+        <v>124273037</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>88359</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7506,39 +7506,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460824</v>
+        <v>460711</v>
       </c>
       <c r="R58" t="n">
-        <v>7051942</v>
+        <v>7052086</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Hackade efter hästmyror</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7600,22 +7600,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124273037</v>
+        <v>124270220</v>
       </c>
       <c r="B59" t="n">
-        <v>88359</v>
+        <v>91299</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7628,39 +7628,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460711</v>
+        <v>460847</v>
       </c>
       <c r="R59" t="n">
-        <v>7052086</v>
+        <v>7051906</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,7 +7687,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7702,12 +7697,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7722,22 +7717,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124270220</v>
+        <v>124274109</v>
       </c>
       <c r="B60" t="n">
-        <v>91299</v>
+        <v>79892</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7750,21 +7745,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7774,13 +7769,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460847</v>
+        <v>460809</v>
       </c>
       <c r="R60" t="n">
-        <v>7051906</v>
+        <v>7051952</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7809,7 +7804,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7819,12 +7814,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7839,22 +7834,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124274109</v>
+        <v>124268557</v>
       </c>
       <c r="B61" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7867,37 +7862,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460809</v>
+        <v>460824</v>
       </c>
       <c r="R61" t="n">
-        <v>7051952</v>
+        <v>7051942</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Hackade efter hästmyror</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,12 +7956,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124268780</v>
+        <v>124269984</v>
       </c>
       <c r="B82" t="n">
-        <v>88359</v>
+        <v>74769</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10509,25 +10509,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>229653</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>460823</v>
+        <v>460724</v>
       </c>
       <c r="R82" t="n">
-        <v>7051631</v>
+        <v>7051694</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På uppstickande rot på granlåga</t>
+          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10614,10 +10614,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124270612</v>
+        <v>124273896</v>
       </c>
       <c r="B83" t="n">
-        <v>82597</v>
+        <v>79920</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10626,41 +10626,46 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>460801</v>
+        <v>460818</v>
       </c>
       <c r="R83" t="n">
-        <v>7051993</v>
+        <v>7051847</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10689,7 +10694,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10699,12 +10704,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På en grov gammal lutande sälg.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10715,26 +10720,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124268429</v>
+        <v>124269872</v>
       </c>
       <c r="B84" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10743,41 +10773,46 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>460855</v>
+        <v>460849</v>
       </c>
       <c r="R84" t="n">
-        <v>7051646</v>
+        <v>7051864</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10806,7 +10841,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10816,12 +10851,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog i ravin</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10836,22 +10871,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124273896</v>
+        <v>124266490</v>
       </c>
       <c r="B85" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10860,46 +10895,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>460818</v>
+        <v>460881</v>
       </c>
       <c r="R85" t="n">
-        <v>7051847</v>
+        <v>7051457</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10928,7 +10958,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10938,12 +10968,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På en grov gammal lutande sälg.</t>
+          <t>På senvuxen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10954,51 +10984,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124269872</v>
+        <v>124269110</v>
       </c>
       <c r="B86" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11007,31 +11012,40 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11040,13 +11054,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>460849</v>
+        <v>460750</v>
       </c>
       <c r="R86" t="n">
-        <v>7051864</v>
+        <v>7051802</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11075,7 +11089,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11085,12 +11099,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Växer i en död smal gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11101,26 +11115,51 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124266490</v>
+        <v>124268628</v>
       </c>
       <c r="B87" t="n">
-        <v>74901</v>
+        <v>79919</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11129,25 +11168,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11157,13 +11196,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>460881</v>
+        <v>460706</v>
       </c>
       <c r="R87" t="n">
-        <v>7051457</v>
+        <v>7051944</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11192,7 +11231,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11202,12 +11241,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På senvuxen gran i gransumpskog</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11218,26 +11252,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124269110</v>
+        <v>124268780</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11250,48 +11289,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>460750</v>
+        <v>460823</v>
       </c>
       <c r="R88" t="n">
-        <v>7051802</v>
+        <v>7051631</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11323,7 +11348,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11333,12 +11358,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Växer i en död smal gran.</t>
+          <t>På uppstickande rot på granlåga</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11349,51 +11374,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124268628</v>
+        <v>124270612</v>
       </c>
       <c r="B89" t="n">
-        <v>79919</v>
+        <v>82597</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11402,25 +11402,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11430,13 +11430,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>460706</v>
+        <v>460801</v>
       </c>
       <c r="R89" t="n">
-        <v>7051944</v>
+        <v>7051993</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11475,7 +11475,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11486,31 +11491,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124266592</v>
+        <v>124268429</v>
       </c>
       <c r="B90" t="n">
-        <v>56714</v>
+        <v>79892</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11523,46 +11523,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>460832</v>
+        <v>460855</v>
       </c>
       <c r="R90" t="n">
-        <v>7051434</v>
+        <v>7051646</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11591,7 +11582,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11601,7 +11592,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog i ravin</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11616,22 +11612,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124269984</v>
+        <v>124266592</v>
       </c>
       <c r="B91" t="n">
-        <v>74769</v>
+        <v>56714</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11640,41 +11636,50 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229653</v>
+        <v>102612</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>460724</v>
+        <v>460832</v>
       </c>
       <c r="R91" t="n">
-        <v>7051694</v>
+        <v>7051434</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11703,7 +11708,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11713,12 +11718,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Tre fruktkroppar på stuplav på sälg,  ca 30 cm i diameter</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11733,22 +11733,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124270241</v>
+        <v>124272422</v>
       </c>
       <c r="B92" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11757,41 +11757,46 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>460847</v>
+        <v>460738</v>
       </c>
       <c r="R92" t="n">
-        <v>7051906</v>
+        <v>7052399</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11820,7 +11825,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11830,12 +11835,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ymnigt, rikligt och fertilt.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11846,23 +11851,48 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124272422</v>
+        <v>124267659</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -11896,24 +11926,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>460738</v>
+        <v>460736</v>
       </c>
       <c r="R93" t="n">
-        <v>7052399</v>
+        <v>7051676</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11942,7 +11967,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11952,12 +11977,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ymnigt, rikligt och fertilt.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12009,7 +12034,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124267659</v>
+        <v>124267327</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -12049,13 +12074,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>460736</v>
+        <v>460755</v>
       </c>
       <c r="R94" t="n">
-        <v>7051676</v>
+        <v>7051597</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12084,7 +12109,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12094,12 +12119,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12151,10 +12171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124267327</v>
+        <v>124270241</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12163,25 +12183,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12191,13 +12211,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>460755</v>
+        <v>460847</v>
       </c>
       <c r="R95" t="n">
-        <v>7051597</v>
+        <v>7051906</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12226,7 +12246,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12236,7 +12256,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12247,41 +12272,16 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -13366,10 +13366,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124267176</v>
+        <v>124271938</v>
       </c>
       <c r="B105" t="n">
-        <v>74893</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13382,37 +13382,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>460874</v>
+        <v>460584</v>
       </c>
       <c r="R105" t="n">
-        <v>7051455</v>
+        <v>7052433</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13462,23 +13462,48 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124271938</v>
+        <v>124268210</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -13511,20 +13536,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>460584</v>
+        <v>460916</v>
       </c>
       <c r="R106" t="n">
-        <v>7052433</v>
+        <v>7051599</v>
       </c>
       <c r="S106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13553,7 +13587,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13563,7 +13597,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13574,51 +13613,26 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124268210</v>
+        <v>124266826</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13627,50 +13641,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>460916</v>
+        <v>460883</v>
       </c>
       <c r="R107" t="n">
-        <v>7051599</v>
+        <v>7051481</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13699,7 +13704,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13709,12 +13714,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13729,22 +13729,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124266826</v>
+        <v>124267176</v>
       </c>
       <c r="B108" t="n">
-        <v>79920</v>
+        <v>74893</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13753,25 +13753,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13781,13 +13781,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>460883</v>
+        <v>460874</v>
       </c>
       <c r="R108" t="n">
-        <v>7051481</v>
+        <v>7051455</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124269436</v>
+        <v>124272912</v>
       </c>
       <c r="B112" t="n">
         <v>57513</v>
@@ -14252,13 +14252,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460863</v>
+        <v>460810</v>
       </c>
       <c r="R112" t="n">
-        <v>7051810</v>
+        <v>7051669</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14317,19 +14317,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124274274</v>
+        <v>124266973</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -14365,22 +14365,27 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460882</v>
+        <v>460809</v>
       </c>
       <c r="R113" t="n">
-        <v>7051627</v>
+        <v>7051526</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14409,7 +14414,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14419,12 +14424,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14476,7 +14481,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124271760</v>
+        <v>124268185</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14522,17 +14527,17 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460645</v>
+        <v>460745</v>
       </c>
       <c r="R114" t="n">
-        <v>7052383</v>
+        <v>7051760</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14561,7 +14566,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14571,12 +14576,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14628,7 +14633,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124266973</v>
+        <v>124272685</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14664,12 +14669,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14678,10 +14678,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460809</v>
+        <v>460814</v>
       </c>
       <c r="R115" t="n">
-        <v>7051526</v>
+        <v>7051693</v>
       </c>
       <c r="S115" t="n">
         <v>8</v>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14723,12 +14723,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14739,48 +14739,23 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124272795</v>
+        <v>124272428</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -14816,7 +14791,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -14825,10 +14800,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460765</v>
+        <v>460778</v>
       </c>
       <c r="R116" t="n">
-        <v>7052225</v>
+        <v>7052106</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14860,7 +14835,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14870,12 +14845,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14902,7 +14877,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124269906</v>
+        <v>124271818</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -14938,27 +14913,22 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460698</v>
+        <v>460809</v>
       </c>
       <c r="R117" t="n">
-        <v>7052021</v>
+        <v>7052003</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14987,7 +14957,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14997,12 +14967,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15013,48 +14983,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124272912</v>
+        <v>124269906</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15090,22 +15035,27 @@
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460810</v>
+        <v>460698</v>
       </c>
       <c r="R118" t="n">
-        <v>7051669</v>
+        <v>7052021</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15134,7 +15084,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15144,12 +15094,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15160,23 +15110,48 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124271818</v>
+        <v>124269436</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15221,13 +15196,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460809</v>
+        <v>460863</v>
       </c>
       <c r="R119" t="n">
-        <v>7052003</v>
+        <v>7051810</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15256,7 +15231,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15266,12 +15241,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15291,14 +15266,14 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124272685</v>
+        <v>124268252</v>
       </c>
       <c r="B120" t="n">
         <v>57513</v>
@@ -15343,13 +15318,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460814</v>
+        <v>460924</v>
       </c>
       <c r="R120" t="n">
-        <v>7051693</v>
+        <v>7051476</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15378,7 +15353,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15388,12 +15363,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15408,19 +15383,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124267188</v>
+        <v>124270215</v>
       </c>
       <c r="B121" t="n">
         <v>57513</v>
@@ -15456,27 +15431,22 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460766</v>
+        <v>460675</v>
       </c>
       <c r="R121" t="n">
-        <v>7051531</v>
+        <v>7052082</v>
       </c>
       <c r="S121" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15505,7 +15475,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15515,12 +15485,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15531,48 +15501,23 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124272428</v>
+        <v>124271760</v>
       </c>
       <c r="B122" t="n">
         <v>57513</v>
@@ -15611,19 +15556,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460778</v>
+        <v>460645</v>
       </c>
       <c r="R122" t="n">
-        <v>7052106</v>
+        <v>7052383</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15652,7 +15602,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15662,12 +15612,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15678,23 +15628,48 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124268252</v>
+        <v>124272795</v>
       </c>
       <c r="B123" t="n">
         <v>57513</v>
@@ -15739,13 +15714,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460924</v>
+        <v>460765</v>
       </c>
       <c r="R123" t="n">
-        <v>7051476</v>
+        <v>7052225</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15774,7 +15749,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15784,12 +15759,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15804,19 +15779,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124270215</v>
+        <v>124274274</v>
       </c>
       <c r="B124" t="n">
         <v>57513</v>
@@ -15852,7 +15827,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15861,13 +15836,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460675</v>
+        <v>460882</v>
       </c>
       <c r="R124" t="n">
-        <v>7052082</v>
+        <v>7051627</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15896,7 +15871,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15906,12 +15881,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15922,23 +15897,48 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124268185</v>
+        <v>124267188</v>
       </c>
       <c r="B125" t="n">
         <v>57513</v>
@@ -15974,7 +15974,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460745</v>
+        <v>460766</v>
       </c>
       <c r="R125" t="n">
-        <v>7051760</v>
+        <v>7051531</v>
       </c>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124272912</v>
+        <v>124272795</v>
       </c>
       <c r="B112" t="n">
         <v>57513</v>
@@ -14252,13 +14252,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460810</v>
+        <v>460765</v>
       </c>
       <c r="R112" t="n">
-        <v>7051669</v>
+        <v>7052225</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14317,19 +14317,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124266973</v>
+        <v>124271760</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -14375,17 +14375,17 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460809</v>
+        <v>460645</v>
       </c>
       <c r="R113" t="n">
-        <v>7051526</v>
+        <v>7052383</v>
       </c>
       <c r="S113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14481,7 +14481,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124268185</v>
+        <v>124272912</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14517,12 +14517,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14531,13 +14526,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460745</v>
+        <v>460810</v>
       </c>
       <c r="R114" t="n">
-        <v>7051760</v>
+        <v>7051669</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14566,7 +14561,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14576,12 +14571,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14592,48 +14587,23 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124272685</v>
+        <v>124272428</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14669,7 +14639,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14678,13 +14648,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460814</v>
+        <v>460778</v>
       </c>
       <c r="R115" t="n">
-        <v>7051693</v>
+        <v>7052106</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14713,7 +14683,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14723,12 +14693,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14743,19 +14713,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124272428</v>
+        <v>124268252</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -14791,7 +14761,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -14800,13 +14770,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460778</v>
+        <v>460924</v>
       </c>
       <c r="R116" t="n">
-        <v>7052106</v>
+        <v>7051476</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14835,7 +14805,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14845,12 +14815,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14865,19 +14835,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124271818</v>
+        <v>124269906</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -14913,22 +14883,27 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460809</v>
+        <v>460698</v>
       </c>
       <c r="R117" t="n">
-        <v>7052003</v>
+        <v>7052021</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14957,7 +14932,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14967,12 +14942,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14983,23 +14958,48 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124269906</v>
+        <v>124267188</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15035,7 +15035,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -15045,17 +15045,17 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460698</v>
+        <v>460766</v>
       </c>
       <c r="R118" t="n">
-        <v>7052021</v>
+        <v>7051531</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15094,12 +15094,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15151,7 +15151,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124269436</v>
+        <v>124274274</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15192,14 +15192,14 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460863</v>
+        <v>460882</v>
       </c>
       <c r="R119" t="n">
-        <v>7051810</v>
+        <v>7051627</v>
       </c>
       <c r="S119" t="n">
         <v>7</v>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15241,12 +15241,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15257,23 +15257,48 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124268252</v>
+        <v>124271818</v>
       </c>
       <c r="B120" t="n">
         <v>57513</v>
@@ -15318,13 +15343,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460924</v>
+        <v>460809</v>
       </c>
       <c r="R120" t="n">
-        <v>7051476</v>
+        <v>7052003</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15353,7 +15378,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15363,12 +15388,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15388,7 +15413,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -15517,7 +15542,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124271760</v>
+        <v>124272685</v>
       </c>
       <c r="B122" t="n">
         <v>57513</v>
@@ -15553,27 +15578,22 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460645</v>
+        <v>460814</v>
       </c>
       <c r="R122" t="n">
-        <v>7052383</v>
+        <v>7051693</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15602,7 +15622,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15612,12 +15632,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15628,48 +15648,23 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124272795</v>
+        <v>124269436</v>
       </c>
       <c r="B123" t="n">
         <v>57513</v>
@@ -15714,13 +15709,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460765</v>
+        <v>460863</v>
       </c>
       <c r="R123" t="n">
-        <v>7052225</v>
+        <v>7051810</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15749,7 +15744,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15759,12 +15754,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15779,19 +15774,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124274274</v>
+        <v>124266973</v>
       </c>
       <c r="B124" t="n">
         <v>57513</v>
@@ -15827,22 +15822,27 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460882</v>
+        <v>460809</v>
       </c>
       <c r="R124" t="n">
-        <v>7051627</v>
+        <v>7051526</v>
       </c>
       <c r="S124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15881,12 +15881,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15938,7 +15938,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124267188</v>
+        <v>124268185</v>
       </c>
       <c r="B125" t="n">
         <v>57513</v>
@@ -15974,7 +15974,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460766</v>
+        <v>460745</v>
       </c>
       <c r="R125" t="n">
-        <v>7051531</v>
+        <v>7051760</v>
       </c>
       <c r="S125" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124272795</v>
+        <v>124270215</v>
       </c>
       <c r="B112" t="n">
         <v>57513</v>
@@ -14243,22 +14243,22 @@
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460765</v>
+        <v>460675</v>
       </c>
       <c r="R112" t="n">
-        <v>7052225</v>
+        <v>7052082</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14317,19 +14317,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124271760</v>
+        <v>124267188</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -14365,7 +14365,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -14375,17 +14375,17 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460645</v>
+        <v>460766</v>
       </c>
       <c r="R113" t="n">
-        <v>7052383</v>
+        <v>7051531</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14481,7 +14481,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124272912</v>
+        <v>124272428</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14517,7 +14517,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14526,13 +14526,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460810</v>
+        <v>460778</v>
       </c>
       <c r="R114" t="n">
-        <v>7051669</v>
+        <v>7052106</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14591,19 +14591,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124272428</v>
+        <v>124269436</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14639,7 +14639,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460778</v>
+        <v>460863</v>
       </c>
       <c r="R115" t="n">
-        <v>7052106</v>
+        <v>7051810</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14713,19 +14713,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124268252</v>
+        <v>124266973</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -14761,7 +14761,12 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -14770,13 +14775,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460924</v>
+        <v>460809</v>
       </c>
       <c r="R116" t="n">
-        <v>7051476</v>
+        <v>7051526</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14805,7 +14810,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14815,12 +14820,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14831,23 +14836,48 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124269906</v>
+        <v>124271760</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -14893,17 +14923,17 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460698</v>
+        <v>460645</v>
       </c>
       <c r="R117" t="n">
-        <v>7052021</v>
+        <v>7052383</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14932,7 +14962,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14942,12 +14972,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14999,7 +15029,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124267188</v>
+        <v>124268185</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15035,7 +15065,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -15049,13 +15079,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460766</v>
+        <v>460745</v>
       </c>
       <c r="R118" t="n">
-        <v>7051531</v>
+        <v>7051760</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15084,7 +15114,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15094,12 +15124,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15151,7 +15181,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124274274</v>
+        <v>124271818</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15192,17 +15222,17 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460882</v>
+        <v>460809</v>
       </c>
       <c r="R119" t="n">
-        <v>7051627</v>
+        <v>7052003</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15231,7 +15261,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15241,12 +15271,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15257,48 +15287,23 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124271818</v>
+        <v>124272912</v>
       </c>
       <c r="B120" t="n">
         <v>57513</v>
@@ -15343,13 +15348,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460809</v>
+        <v>460810</v>
       </c>
       <c r="R120" t="n">
-        <v>7052003</v>
+        <v>7051669</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15378,7 +15383,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15388,12 +15393,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15408,19 +15413,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124270215</v>
+        <v>124268252</v>
       </c>
       <c r="B121" t="n">
         <v>57513</v>
@@ -15456,22 +15461,22 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460675</v>
+        <v>460924</v>
       </c>
       <c r="R121" t="n">
-        <v>7052082</v>
+        <v>7051476</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15500,7 +15505,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15510,12 +15515,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15530,19 +15535,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124272685</v>
+        <v>124272795</v>
       </c>
       <c r="B122" t="n">
         <v>57513</v>
@@ -15587,13 +15592,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460814</v>
+        <v>460765</v>
       </c>
       <c r="R122" t="n">
-        <v>7051693</v>
+        <v>7052225</v>
       </c>
       <c r="S122" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15622,7 +15627,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15632,12 +15637,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15652,19 +15657,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124269436</v>
+        <v>124274274</v>
       </c>
       <c r="B123" t="n">
         <v>57513</v>
@@ -15705,14 +15710,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460863</v>
+        <v>460882</v>
       </c>
       <c r="R123" t="n">
-        <v>7051810</v>
+        <v>7051627</v>
       </c>
       <c r="S123" t="n">
         <v>7</v>
@@ -15744,7 +15749,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15754,12 +15759,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15770,23 +15775,48 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124266973</v>
+        <v>124272685</v>
       </c>
       <c r="B124" t="n">
         <v>57513</v>
@@ -15822,12 +15852,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15836,10 +15861,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460809</v>
+        <v>460814</v>
       </c>
       <c r="R124" t="n">
-        <v>7051526</v>
+        <v>7051693</v>
       </c>
       <c r="S124" t="n">
         <v>8</v>
@@ -15871,7 +15896,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15881,12 +15906,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15897,48 +15922,23 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124268185</v>
+        <v>124269906</v>
       </c>
       <c r="B125" t="n">
         <v>57513</v>
@@ -15984,17 +15984,17 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460745</v>
+        <v>460698</v>
       </c>
       <c r="R125" t="n">
-        <v>7051760</v>
+        <v>7052021</v>
       </c>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124270215</v>
+        <v>124272428</v>
       </c>
       <c r="B112" t="n">
         <v>57513</v>
@@ -14248,17 +14248,17 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460675</v>
+        <v>460778</v>
       </c>
       <c r="R112" t="n">
-        <v>7052082</v>
+        <v>7052106</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14317,12 +14317,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124272428</v>
+        <v>124269906</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14520,16 +14520,21 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460778</v>
+        <v>460698</v>
       </c>
       <c r="R114" t="n">
-        <v>7052106</v>
+        <v>7052021</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14561,7 +14566,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14571,12 +14576,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14587,23 +14592,48 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124269436</v>
+        <v>124268185</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14639,7 +14669,12 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14648,13 +14683,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460863</v>
+        <v>460745</v>
       </c>
       <c r="R115" t="n">
-        <v>7051810</v>
+        <v>7051760</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14683,7 +14718,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14693,12 +14728,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14709,23 +14744,48 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124266973</v>
+        <v>124274274</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -14761,27 +14821,22 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460809</v>
+        <v>460882</v>
       </c>
       <c r="R116" t="n">
-        <v>7051526</v>
+        <v>7051627</v>
       </c>
       <c r="S116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14810,7 +14865,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14820,12 +14875,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14877,7 +14932,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124271760</v>
+        <v>124272912</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -14913,27 +14968,22 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460645</v>
+        <v>460810</v>
       </c>
       <c r="R117" t="n">
-        <v>7052383</v>
+        <v>7051669</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14962,7 +15012,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14972,12 +15022,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14988,48 +15038,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124268185</v>
+        <v>124272685</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15065,12 +15090,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -15079,13 +15099,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460745</v>
+        <v>460814</v>
       </c>
       <c r="R118" t="n">
-        <v>7051760</v>
+        <v>7051693</v>
       </c>
       <c r="S118" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15114,7 +15134,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15124,12 +15144,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15140,48 +15160,23 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124271818</v>
+        <v>124271760</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15217,22 +15212,27 @@
       <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460809</v>
+        <v>460645</v>
       </c>
       <c r="R119" t="n">
-        <v>7052003</v>
+        <v>7052383</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15271,12 +15271,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15287,23 +15287,48 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124272912</v>
+        <v>124266973</v>
       </c>
       <c r="B120" t="n">
         <v>57513</v>
@@ -15339,7 +15364,12 @@
       <c r="I120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15348,13 +15378,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460810</v>
+        <v>460809</v>
       </c>
       <c r="R120" t="n">
-        <v>7051669</v>
+        <v>7051526</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15383,7 +15413,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15393,12 +15423,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15409,16 +15439,41 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -15547,7 +15602,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124272795</v>
+        <v>124271818</v>
       </c>
       <c r="B122" t="n">
         <v>57513</v>
@@ -15592,13 +15647,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460765</v>
+        <v>460809</v>
       </c>
       <c r="R122" t="n">
-        <v>7052225</v>
+        <v>7052003</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15627,7 +15682,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15637,12 +15692,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15657,19 +15712,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124274274</v>
+        <v>124269436</v>
       </c>
       <c r="B123" t="n">
         <v>57513</v>
@@ -15710,14 +15765,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460882</v>
+        <v>460863</v>
       </c>
       <c r="R123" t="n">
-        <v>7051627</v>
+        <v>7051810</v>
       </c>
       <c r="S123" t="n">
         <v>7</v>
@@ -15749,7 +15804,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15759,12 +15814,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15775,48 +15830,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124272685</v>
+        <v>124270215</v>
       </c>
       <c r="B124" t="n">
         <v>57513</v>
@@ -15852,22 +15882,22 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460814</v>
+        <v>460675</v>
       </c>
       <c r="R124" t="n">
-        <v>7051693</v>
+        <v>7052082</v>
       </c>
       <c r="S124" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15896,7 +15926,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15906,12 +15936,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15926,19 +15956,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124269906</v>
+        <v>124272795</v>
       </c>
       <c r="B125" t="n">
         <v>57513</v>
@@ -15974,24 +16004,19 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460698</v>
+        <v>460765</v>
       </c>
       <c r="R125" t="n">
-        <v>7052021</v>
+        <v>7052225</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16023,7 +16048,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16033,12 +16058,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16049,41 +16074,16 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124272428</v>
+        <v>124268185</v>
       </c>
       <c r="B112" t="n">
         <v>57513</v>
@@ -14246,19 +14246,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460778</v>
+        <v>460745</v>
       </c>
       <c r="R112" t="n">
-        <v>7052106</v>
+        <v>7051760</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14292,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14302,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14313,23 +14318,48 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124267188</v>
+        <v>124268252</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -14368,24 +14398,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460766</v>
+        <v>460924</v>
       </c>
       <c r="R113" t="n">
-        <v>7051531</v>
+        <v>7051476</v>
       </c>
       <c r="S113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14414,7 +14439,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14424,12 +14449,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14440,48 +14465,23 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124269906</v>
+        <v>124274274</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -14517,12 +14517,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14531,13 +14526,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460698</v>
+        <v>460882</v>
       </c>
       <c r="R114" t="n">
-        <v>7052021</v>
+        <v>7051627</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14566,7 +14561,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14576,12 +14571,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14633,7 +14628,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124268185</v>
+        <v>124269436</v>
       </c>
       <c r="B115" t="n">
         <v>57513</v>
@@ -14669,12 +14664,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14683,13 +14673,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460745</v>
+        <v>460863</v>
       </c>
       <c r="R115" t="n">
-        <v>7051760</v>
+        <v>7051810</v>
       </c>
       <c r="S115" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14718,7 +14708,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14728,12 +14718,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14744,48 +14734,23 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124274274</v>
+        <v>124272912</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -14826,17 +14791,17 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460882</v>
+        <v>460810</v>
       </c>
       <c r="R116" t="n">
-        <v>7051627</v>
+        <v>7051669</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14865,7 +14830,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14875,12 +14840,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14891,48 +14856,23 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124272912</v>
+        <v>124269906</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -14968,22 +14908,27 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460810</v>
+        <v>460698</v>
       </c>
       <c r="R117" t="n">
-        <v>7051669</v>
+        <v>7052021</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -15012,7 +14957,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15022,12 +14967,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15038,23 +14983,48 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124272685</v>
+        <v>124270215</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15090,22 +15060,22 @@
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460814</v>
+        <v>460675</v>
       </c>
       <c r="R118" t="n">
-        <v>7051693</v>
+        <v>7052082</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15134,7 +15104,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15144,12 +15114,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15164,19 +15134,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124271760</v>
+        <v>124272795</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15212,27 +15182,22 @@
       <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460645</v>
+        <v>460765</v>
       </c>
       <c r="R119" t="n">
-        <v>7052383</v>
+        <v>7052225</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15261,7 +15226,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15271,12 +15236,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15287,41 +15252,16 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -15480,7 +15420,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124268252</v>
+        <v>124271818</v>
       </c>
       <c r="B121" t="n">
         <v>57513</v>
@@ -15525,13 +15465,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460924</v>
+        <v>460809</v>
       </c>
       <c r="R121" t="n">
-        <v>7051476</v>
+        <v>7052003</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15560,7 +15500,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15570,12 +15510,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15595,14 +15535,14 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124271818</v>
+        <v>124272428</v>
       </c>
       <c r="B122" t="n">
         <v>57513</v>
@@ -15638,7 +15578,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15647,13 +15587,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460809</v>
+        <v>460778</v>
       </c>
       <c r="R122" t="n">
-        <v>7052003</v>
+        <v>7052106</v>
       </c>
       <c r="S122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15682,7 +15622,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15692,12 +15632,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15712,19 +15652,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124269436</v>
+        <v>124267188</v>
       </c>
       <c r="B123" t="n">
         <v>57513</v>
@@ -15763,19 +15703,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460863</v>
+        <v>460766</v>
       </c>
       <c r="R123" t="n">
-        <v>7051810</v>
+        <v>7051531</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15804,7 +15749,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15814,12 +15759,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15830,23 +15775,48 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124270215</v>
+        <v>124272685</v>
       </c>
       <c r="B124" t="n">
         <v>57513</v>
@@ -15882,22 +15852,22 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460675</v>
+        <v>460814</v>
       </c>
       <c r="R124" t="n">
-        <v>7052082</v>
+        <v>7051693</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15926,7 +15896,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15936,12 +15906,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15956,19 +15926,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124272795</v>
+        <v>124271760</v>
       </c>
       <c r="B125" t="n">
         <v>57513</v>
@@ -16004,22 +15974,27 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460765</v>
+        <v>460645</v>
       </c>
       <c r="R125" t="n">
-        <v>7052225</v>
+        <v>7052383</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16048,7 +16023,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16058,12 +16033,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16074,16 +16049,41 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,10 +14207,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124268185</v>
+        <v>124274274</v>
       </c>
       <c r="B112" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14243,27 +14243,22 @@
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460745</v>
+        <v>460882</v>
       </c>
       <c r="R112" t="n">
-        <v>7051760</v>
+        <v>7051627</v>
       </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14292,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14302,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14359,10 +14354,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124268252</v>
+        <v>124272912</v>
       </c>
       <c r="B113" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14404,10 +14399,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460924</v>
+        <v>460810</v>
       </c>
       <c r="R113" t="n">
-        <v>7051476</v>
+        <v>7051669</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -14439,7 +14434,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14449,12 +14444,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14469,22 +14464,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124274274</v>
+        <v>124267188</v>
       </c>
       <c r="B114" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14520,19 +14515,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460882</v>
+        <v>460766</v>
       </c>
       <c r="R114" t="n">
-        <v>7051627</v>
+        <v>7051531</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14628,10 +14628,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124269436</v>
+        <v>124266973</v>
       </c>
       <c r="B115" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14664,7 +14664,12 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14673,13 +14678,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>460863</v>
+        <v>460809</v>
       </c>
       <c r="R115" t="n">
-        <v>7051810</v>
+        <v>7051526</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14708,7 +14713,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14718,12 +14723,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14734,26 +14739,51 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124272912</v>
+        <v>124272685</v>
       </c>
       <c r="B116" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14795,13 +14825,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460810</v>
+        <v>460814</v>
       </c>
       <c r="R116" t="n">
-        <v>7051669</v>
+        <v>7051693</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14830,7 +14860,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14840,12 +14870,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14872,10 +14902,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124269906</v>
+        <v>124268185</v>
       </c>
       <c r="B117" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14918,17 +14948,17 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460698</v>
+        <v>460745</v>
       </c>
       <c r="R117" t="n">
-        <v>7052021</v>
+        <v>7051760</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14957,7 +14987,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14967,12 +14997,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15024,10 +15054,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124270215</v>
+        <v>124271760</v>
       </c>
       <c r="B118" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15063,19 +15093,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>460675</v>
+        <v>460645</v>
       </c>
       <c r="R118" t="n">
-        <v>7052082</v>
+        <v>7052383</v>
       </c>
       <c r="S118" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15104,7 +15139,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15114,12 +15149,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15130,16 +15165,41 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -15149,7 +15209,7 @@
         <v>124272795</v>
       </c>
       <c r="B119" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15268,10 +15328,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124266973</v>
+        <v>124271818</v>
       </c>
       <c r="B120" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15304,12 +15364,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15321,10 +15376,10 @@
         <v>460809</v>
       </c>
       <c r="R120" t="n">
-        <v>7051526</v>
+        <v>7052003</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15353,7 +15408,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15363,12 +15418,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, relativt rikligt på en gran.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15379,51 +15434,26 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124271818</v>
+        <v>124268252</v>
       </c>
       <c r="B121" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15465,13 +15495,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460809</v>
+        <v>460924</v>
       </c>
       <c r="R121" t="n">
-        <v>7052003</v>
+        <v>7051476</v>
       </c>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15500,7 +15530,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15510,12 +15540,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15535,7 +15565,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -15545,7 +15575,7 @@
         <v>124272428</v>
       </c>
       <c r="B122" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15664,10 +15694,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124267188</v>
+        <v>124269906</v>
       </c>
       <c r="B123" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15700,7 +15730,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -15710,17 +15740,17 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460766</v>
+        <v>460698</v>
       </c>
       <c r="R123" t="n">
-        <v>7051531</v>
+        <v>7052021</v>
       </c>
       <c r="S123" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15749,7 +15779,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15759,12 +15789,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15816,10 +15846,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124272685</v>
+        <v>124270215</v>
       </c>
       <c r="B124" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15852,22 +15882,22 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460814</v>
+        <v>460675</v>
       </c>
       <c r="R124" t="n">
-        <v>7051693</v>
+        <v>7052082</v>
       </c>
       <c r="S124" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15896,7 +15926,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15906,12 +15936,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15926,22 +15956,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124271760</v>
+        <v>124269436</v>
       </c>
       <c r="B125" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15974,24 +16004,19 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460645</v>
+        <v>460863</v>
       </c>
       <c r="R125" t="n">
-        <v>7052383</v>
+        <v>7051810</v>
       </c>
       <c r="S125" t="n">
         <v>7</v>
@@ -16023,7 +16048,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16033,12 +16058,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, där de färskaste ringhacken troligen är skapade 2025.</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16049,41 +16074,16 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 12508-2025 artfynd.xlsx
+++ b/artfynd/A 12508-2025 artfynd.xlsx
@@ -14207,7 +14207,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124274274</v>
+        <v>124272685</v>
       </c>
       <c r="B112" t="n">
         <v>57635</v>
@@ -14248,17 +14248,17 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460882</v>
+        <v>460814</v>
       </c>
       <c r="R112" t="n">
-        <v>7051627</v>
+        <v>7051693</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringbarkning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14313,48 +14313,23 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124272912</v>
+        <v>124268185</v>
       </c>
       <c r="B113" t="n">
         <v>57635</v>
@@ -14390,7 +14365,12 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14399,13 +14379,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>460810</v>
+        <v>460745</v>
       </c>
       <c r="R113" t="n">
-        <v>7051669</v>
+        <v>7051760</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14434,7 +14414,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14444,12 +14424,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14460,23 +14440,48 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124267188</v>
+        <v>124268252</v>
       </c>
       <c r="B114" t="n">
         <v>57635</v>
@@ -14515,24 +14520,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>460766</v>
+        <v>460924</v>
       </c>
       <c r="R114" t="n">
-        <v>7051531</v>
+        <v>7051476</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
+          <t>Tretåig hackspett ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14587,41 +14587,16 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14780,7 +14755,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124272685</v>
+        <v>124269436</v>
       </c>
       <c r="B116" t="n">
         <v>57635</v>
@@ -14825,13 +14800,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>460814</v>
+        <v>460863</v>
       </c>
       <c r="R116" t="n">
-        <v>7051693</v>
+        <v>7051810</v>
       </c>
       <c r="S116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14860,7 +14835,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14870,12 +14845,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringbarkning</t>
+          <t>Ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14890,19 +14865,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124268185</v>
+        <v>124272795</v>
       </c>
       <c r="B117" t="n">
         <v>57635</v>
@@ -14938,12 +14913,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14952,13 +14922,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>460745</v>
+        <v>460765</v>
       </c>
       <c r="R117" t="n">
-        <v>7051760</v>
+        <v>7052225</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14987,7 +14957,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14997,12 +14967,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs ca 6 meter på en granstam i gammal luckig granskog.</t>
+          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15013,41 +14983,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -15206,7 +15151,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124272795</v>
+        <v>124270215</v>
       </c>
       <c r="B119" t="n">
         <v>57635</v>
@@ -15242,22 +15187,22 @@
       <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>460765</v>
+        <v>460675</v>
       </c>
       <c r="R119" t="n">
-        <v>7052225</v>
+        <v>7052082</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15286,7 +15231,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15296,12 +15241,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, halvgamla på gammal levande gran i gammal granskog</t>
+          <t>Ringhack färska o äldre på gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15316,19 +15261,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johanna Jonsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124271818</v>
+        <v>124267188</v>
       </c>
       <c r="B120" t="n">
         <v>57635</v>
@@ -15367,19 +15312,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>460809</v>
+        <v>460766</v>
       </c>
       <c r="R120" t="n">
-        <v>7052003</v>
+        <v>7051531</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15408,7 +15358,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15418,12 +15368,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack, äldre, på naturhänsyn-snitslad gran.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15434,23 +15384,48 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124268252</v>
+        <v>124272428</v>
       </c>
       <c r="B121" t="n">
         <v>57635</v>
@@ -15486,7 +15461,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -15495,13 +15470,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>460924</v>
+        <v>460778</v>
       </c>
       <c r="R121" t="n">
-        <v>7051476</v>
+        <v>7052106</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15530,7 +15505,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15540,12 +15515,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett ringhack</t>
+          <t>Ringhack på rejält gammal gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15560,19 +15535,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124272428</v>
+        <v>124269906</v>
       </c>
       <c r="B122" t="n">
         <v>57635</v>
@@ -15611,16 +15586,21 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>460778</v>
+        <v>460698</v>
       </c>
       <c r="R122" t="n">
-        <v>7052106</v>
+        <v>7052021</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15652,7 +15632,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15662,12 +15642,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack på rejält gammal gran</t>
+          <t>Ringhack, enstaka färska och fler äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15678,23 +15658,48 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124269906</v>
+        <v>124272912</v>
       </c>
       <c r="B123" t="n">
         <v>57635</v>
@@ -15730,27 +15735,22 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>460698</v>
+        <v>460810</v>
       </c>
       <c r="R123" t="n">
-        <v>7052021</v>
+        <v>7051669</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och fler äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15805,48 +15805,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124270215</v>
+        <v>124274274</v>
       </c>
       <c r="B124" t="n">
         <v>57635</v>
@@ -15882,7 +15857,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15891,13 +15866,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>460675</v>
+        <v>460882</v>
       </c>
       <c r="R124" t="n">
-        <v>7052082</v>
+        <v>7051627</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15926,7 +15901,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15936,12 +15911,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack färska o äldre på gran</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15952,23 +15927,48 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johanna Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124269436</v>
+        <v>124271818</v>
       </c>
       <c r="B125" t="n">
         <v>57635</v>
@@ -16013,13 +16013,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>460863</v>
+        <v>460809</v>
       </c>
       <c r="R125" t="n">
-        <v>7051810</v>
+        <v>7052003</v>
       </c>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -16058,12 +16058,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
